--- a/data/trans_bre/P62-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P62-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -16,49</t>
+          <t>-43,43; -15,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -7,01</t>
+          <t>-33,82; -9,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,14; -14,82</t>
+          <t>-38,17; -14,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,72; -6,53</t>
+          <t>-27,65; -6,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,35; -23,0</t>
+          <t>-54,38; -22,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,77; -15,95</t>
+          <t>-57,53; -20,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,13; -24,17</t>
+          <t>-55,67; -23,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -11,15</t>
+          <t>-38,72; -10,1</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,27; -49,99</t>
+          <t>-72,24; -50,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,05; -25,94</t>
+          <t>-47,8; -24,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,22; -25,47</t>
+          <t>-49,71; -27,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,42; -15,89</t>
+          <t>-34,95; -16,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,89; -65,85</t>
+          <t>-85,23; -67,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,69; -47,29</t>
+          <t>-74,06; -45,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,08; -47,59</t>
+          <t>-75,5; -50,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,28; -23,1</t>
+          <t>-45,56; -23,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-63,93; -44,12</t>
+          <t>-63,29; -42,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,31; -1,85</t>
+          <t>-22,13; -1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 3,96</t>
+          <t>-19,65; 4,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,91; -8,26</t>
+          <t>-27,92; -7,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,59; -62,69</t>
+          <t>-82,34; -61,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,8; -3,68</t>
+          <t>-39,52; -3,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 6,54</t>
+          <t>-32,47; 7,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,13; -12,02</t>
+          <t>-36,99; -11,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,53; -34,51</t>
+          <t>-46,44; -34,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,23; -17,35</t>
+          <t>-28,34; -16,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,06; -14,42</t>
+          <t>-26,11; -13,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 25,71</t>
+          <t>-27,7; 22,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,79; -51,97</t>
+          <t>-66,14; -52,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,0; -37,94</t>
+          <t>-56,44; -36,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,99; -29,1</t>
+          <t>-47,72; -27,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 45,93</t>
+          <t>-43,73; 37,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,39; -12,88</t>
+          <t>-31,98; -12,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 2,93</t>
+          <t>-11,13; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -0,03</t>
+          <t>-12,88; -0,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -4,51</t>
+          <t>-20,11; -5,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,44; -29,13</t>
+          <t>-55,84; -28,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 7,43</t>
+          <t>-23,81; 6,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,7; -0,12</t>
+          <t>-25,88; -0,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,73; -8,36</t>
+          <t>-30,66; -10,07</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,04; 21,34</t>
+          <t>15,38; 21,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,75; 22,1</t>
+          <t>13,85; 22,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 23,8</t>
+          <t>16,61; 23,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,3; 25,27</t>
+          <t>17,25; 25,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>247,28; 1230,31</t>
+          <t>248,38; 1184,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137,16; 613,04</t>
+          <t>139,72; 598,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>319,03; 1849,9</t>
+          <t>293,19; 1601,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>202,44; 1022,32</t>
+          <t>212,42; 1036,19</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-33,12; -26,81</t>
+          <t>-33,25; -26,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,93; -12,1</t>
+          <t>-17,92; -11,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -13,23</t>
+          <t>-18,93; -13,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 4,85</t>
+          <t>-18,86; 4,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,54; -50,82</t>
+          <t>-58,6; -50,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,35; -28,69</t>
+          <t>-39,28; -28,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,82; -29,75</t>
+          <t>-39,81; -29,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 9,04</t>
+          <t>-33,61; 7,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P62-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P62-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-18,06</t>
+          <t>-20,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-26,72%</t>
+          <t>-29,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,43; -15,59</t>
+          <t>-43,89; -17,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -9,63</t>
+          <t>-34,78; -6,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,17; -14,6</t>
+          <t>-38,56; -14,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,65; -6,27</t>
+          <t>-31,0; -10,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -22,07</t>
+          <t>-53,4; -23,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,53; -20,26</t>
+          <t>-58,5; -14,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,67; -23,59</t>
+          <t>-55,76; -23,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,72; -10,1</t>
+          <t>-41,62; -17,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-25,6</t>
+          <t>-25,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-35,11%</t>
+          <t>-34,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,24; -50,93</t>
+          <t>-71,99; -50,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,8; -24,5</t>
+          <t>-47,38; -25,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,71; -27,44</t>
+          <t>-49,04; -26,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,95; -16,21</t>
+          <t>-34,15; -15,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -67,33</t>
+          <t>-85,12; -67,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,06; -45,71</t>
+          <t>-74,18; -47,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,5; -50,64</t>
+          <t>-75,02; -50,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,56; -23,72</t>
+          <t>-44,86; -22,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,33</t>
+          <t>-17,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-24,96%</t>
+          <t>-24,65%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-63,29; -42,59</t>
+          <t>-64,18; -43,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,13; -1,45</t>
+          <t>-22,66; -2,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 4,32</t>
+          <t>-19,28; 5,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,92; -7,9</t>
+          <t>-26,92; -7,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,34; -61,13</t>
+          <t>-82,79; -60,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -3,14</t>
+          <t>-40,86; -5,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 7,78</t>
+          <t>-31,6; 9,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,99; -11,76</t>
+          <t>-35,97; -11,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-26,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-3,1%</t>
+          <t>-42,24%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,44; -34,98</t>
+          <t>-46,33; -34,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,34; -16,76</t>
+          <t>-28,15; -17,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -13,82</t>
+          <t>-26,35; -14,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 22,36</t>
+          <t>-32,56; -20,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,14; -52,53</t>
+          <t>-65,23; -52,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,44; -36,97</t>
+          <t>-56,0; -37,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -27,53</t>
+          <t>-48,32; -29,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 37,69</t>
+          <t>-49,71; -34,59</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>-11,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-20,7%</t>
+          <t>-19,88%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,98; -12,34</t>
+          <t>-31,05; -14,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 2,61</t>
+          <t>-10,08; 2,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -0,11</t>
+          <t>-13,07; -0,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -5,39</t>
+          <t>-18,46; -3,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,84; -28,26</t>
+          <t>-56,12; -31,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 6,77</t>
+          <t>-21,1; 7,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,88; -0,39</t>
+          <t>-26,82; -0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,66; -10,07</t>
+          <t>-29,01; -7,63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,51</t>
+          <t>20,88</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>471,41%</t>
+          <t>469,09%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 21,7</t>
+          <t>15,17; 21,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,85; 22,04</t>
+          <t>13,35; 22,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,61; 23,69</t>
+          <t>16,57; 23,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 25,22</t>
+          <t>16,29; 24,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>248,38; 1184,22</t>
+          <t>221,32; 1101,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>139,72; 598,25</t>
+          <t>132,63; 631,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>293,19; 1601,03</t>
+          <t>297,34; 1559,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>212,42; 1036,19</t>
+          <t>207,33; 1015,6</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-11,68</t>
+          <t>-19,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-21,09%</t>
+          <t>-33,96%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-33,25; -26,7</t>
+          <t>-33,01; -26,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,92; -11,86</t>
+          <t>-17,91; -11,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -13,12</t>
+          <t>-18,91; -12,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 4,16</t>
+          <t>-22,36; -15,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,6; -50,75</t>
+          <t>-58,51; -50,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -28,11</t>
+          <t>-39,24; -27,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -29,29</t>
+          <t>-39,56; -29,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 7,66</t>
+          <t>-38,48; -29,03</t>
         </is>
       </c>
     </row>
